--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:08</t>
+    <t xml:space="preserve">2026-09-09 23:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:01</t>
+    <t xml:space="preserve">2026-09-17 13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:59</t>
+    <t xml:space="preserve">2026-09-23 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:28</t>
+    <t xml:space="preserve">2026-10-02 13:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_nuble.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Coelemu</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Quillón</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:52</t>
+    <t xml:space="preserve">2026-10-04 08:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:49</t>
+    <t xml:space="preserve">2026-10-05 10:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -629,7 +629,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>622526.62</v>
+        <v>622526.63</v>
       </c>
     </row>
     <row r="8">
@@ -765,7 +765,7 @@
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>574072.12</v>
+        <v>574072.13</v>
       </c>
     </row>
     <row r="16">
@@ -816,7 +816,7 @@
         <v>2019</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>539436.62</v>
+        <v>539436.63</v>
       </c>
     </row>
     <row r="19">
